--- a/diseases/d037/1995-1999.xlsx
+++ b/diseases/d037/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22164,7 +22164,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23345,7 +23345,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25707,7 +25707,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26888,7 +26888,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -28069,7 +28069,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -29250,7 +29250,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -30431,7 +30431,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32793,7 +32793,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -35155,7 +35155,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37907,7 +37907,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -39088,7 +39088,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41450,7 +41450,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42631,7 +42631,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43812,7 +43812,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44993,7 +44993,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -46174,7 +46174,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47355,7 +47355,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -48536,7 +48536,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49717,7 +49717,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -51288,7 +51288,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -52469,7 +52469,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -53650,7 +53650,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54831,7 +54831,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -56012,7 +56012,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -57193,7 +57193,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -58374,7 +58374,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -59555,7 +59555,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -60736,7 +60736,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -61917,7 +61917,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -63098,7 +63098,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -64279,7 +64279,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN323" t="b">

--- a/diseases/d037/1995-1999.xlsx
+++ b/diseases/d037/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21543,6 +21543,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22164,7 +22169,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22724,6 +22729,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23345,7 +23355,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23905,6 +23915,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24526,7 +24541,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25086,6 +25101,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25707,7 +25727,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26267,6 +26287,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26888,7 +26913,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27448,6 +27473,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28069,7 +28099,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28629,6 +28659,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29250,7 +29285,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29810,6 +29845,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30431,7 +30471,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30991,6 +31031,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31612,7 +31657,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32172,6 +32217,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32793,7 +32843,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33353,6 +33403,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33974,7 +34029,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34534,6 +34589,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35155,7 +35215,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -36105,6 +36165,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36726,7 +36791,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37286,6 +37351,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37907,7 +37977,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38467,6 +38537,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39088,7 +39163,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39648,6 +39723,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40269,7 +40349,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40829,6 +40909,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41450,7 +41535,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42010,6 +42095,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42631,7 +42721,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43191,6 +43281,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43812,7 +43907,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44372,6 +44467,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44993,7 +45093,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45553,6 +45653,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46174,7 +46279,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46734,6 +46839,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47355,7 +47465,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47915,6 +48025,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48536,7 +48651,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49096,6 +49211,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49717,7 +49837,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -50667,6 +50787,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51288,7 +51413,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51848,6 +51973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52469,7 +52599,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -53029,6 +53159,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53650,7 +53785,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54210,6 +54345,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54831,7 +54971,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -55391,6 +55531,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56012,7 +56157,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -56572,6 +56717,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57193,7 +57343,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -57753,6 +57903,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58374,7 +58529,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58934,6 +59089,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59555,7 +59715,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -60115,6 +60275,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60736,7 +60901,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -61296,6 +61461,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61917,7 +62087,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -62477,6 +62647,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63098,7 +63273,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -63658,6 +63833,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64279,7 +64459,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN323" t="b">

--- a/diseases/d037/1995-1999.xlsx
+++ b/diseases/d037/1995-1999.xlsx
@@ -21538,6 +21538,11 @@
       <c r="Q106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21550,13 +21555,23 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22709,6 +22724,11 @@
       <c r="Q112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22721,13 +22741,23 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
       </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV112" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23880,6 +23910,11 @@
       <c r="Q118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23892,13 +23927,23 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
       </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV118" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25051,6 +25096,11 @@
       <c r="Q124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25063,13 +25113,23 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
       </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV124" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26222,6 +26282,11 @@
       <c r="Q130" t="n">
         <v>0</v>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26234,13 +26299,23 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
       </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV130" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27393,6 +27468,11 @@
       <c r="Q136" t="n">
         <v>0</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27405,13 +27485,23 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
       </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV136" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28564,6 +28654,11 @@
       <c r="Q142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28576,13 +28671,23 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
       </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV142" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29735,6 +29840,11 @@
       <c r="Q148" t="n">
         <v>0</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29747,13 +29857,23 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
       </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV148" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -30906,6 +31026,11 @@
       <c r="Q154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30918,13 +31043,23 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
       </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV154" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32077,6 +32212,11 @@
       <c r="Q160" t="n">
         <v>0</v>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32089,13 +32229,23 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
       </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV160" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33248,6 +33398,11 @@
       <c r="Q166" t="n">
         <v>0</v>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33260,13 +33415,23 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
       </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV166" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34419,6 +34584,11 @@
       <c r="Q172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34431,13 +34601,23 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
       </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV172" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -35980,6 +36160,11 @@
       <c r="Q180" t="n">
         <v>0</v>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35992,13 +36177,23 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
       </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV180" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37151,6 +37346,11 @@
       <c r="Q186" t="n">
         <v>0</v>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37163,13 +37363,23 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
       </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV186" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -38322,6 +38532,11 @@
       <c r="Q192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38334,13 +38549,23 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
       </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV192" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39493,6 +39718,11 @@
       <c r="Q198" t="n">
         <v>0</v>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39505,13 +39735,23 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
       </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV198" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -40664,6 +40904,11 @@
       <c r="Q204" t="n">
         <v>0</v>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40676,13 +40921,23 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
       </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV204" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -41835,6 +42090,11 @@
       <c r="Q210" t="n">
         <v>0</v>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41847,13 +42107,23 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
       </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV210" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -43006,6 +43276,11 @@
       <c r="Q216" t="n">
         <v>0</v>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43018,13 +43293,23 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
       </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV216" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -44177,6 +44462,11 @@
       <c r="Q222" t="n">
         <v>0</v>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44189,13 +44479,23 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
       </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV222" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -45348,6 +45648,11 @@
       <c r="Q228" t="n">
         <v>0</v>
       </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45360,13 +45665,23 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
         <v>0</v>
       </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV228" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -46519,6 +46834,11 @@
       <c r="Q234" t="n">
         <v>0</v>
       </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46531,13 +46851,23 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
         <v>0</v>
       </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV234" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -47690,6 +48020,11 @@
       <c r="Q240" t="n">
         <v>0</v>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47702,13 +48037,23 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
         <v>0</v>
       </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV240" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -48861,6 +49206,11 @@
       <c r="Q246" t="n">
         <v>0</v>
       </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48873,13 +49223,23 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
         <v>0</v>
       </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV246" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -50422,6 +50782,11 @@
       <c r="Q254" t="n">
         <v>0</v>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50434,13 +50799,23 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
         <v>0</v>
       </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV254" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -51593,6 +51968,11 @@
       <c r="Q260" t="n">
         <v>0</v>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51605,13 +51985,23 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
         <v>0</v>
       </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV260" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -52764,6 +53154,11 @@
       <c r="Q266" t="n">
         <v>0</v>
       </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52776,13 +53171,23 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
         <v>0</v>
       </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV266" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -53935,6 +54340,11 @@
       <c r="Q272" t="n">
         <v>0</v>
       </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53947,13 +54357,23 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS272" t="inlineStr"/>
       <c r="AT272" t="n">
         <v>0</v>
       </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV272" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -55106,6 +55526,11 @@
       <c r="Q278" t="n">
         <v>0</v>
       </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -55118,13 +55543,23 @@
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
         <v>0</v>
       </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV278" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -56277,6 +56712,11 @@
       <c r="Q284" t="n">
         <v>0</v>
       </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -56289,13 +56729,23 @@
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS284" t="inlineStr"/>
       <c r="AT284" t="n">
         <v>0</v>
       </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV284" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -57448,6 +57898,11 @@
       <c r="Q290" t="n">
         <v>0</v>
       </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA290" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57460,13 +57915,23 @@
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS290" t="inlineStr"/>
       <c r="AT290" t="n">
         <v>0</v>
       </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV290" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -58619,6 +59084,11 @@
       <c r="Q296" t="n">
         <v>0</v>
       </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58631,13 +59101,23 @@
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS296" t="inlineStr"/>
       <c r="AT296" t="n">
         <v>0</v>
       </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV296" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -59790,6 +60270,11 @@
       <c r="Q302" t="n">
         <v>0</v>
       </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA302" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -59802,13 +60287,23 @@
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR302" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS302" t="inlineStr"/>
       <c r="AT302" t="n">
         <v>0</v>
       </c>
+      <c r="AU302" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV302" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -60961,6 +61456,11 @@
       <c r="Q308" t="n">
         <v>0</v>
       </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA308" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60973,13 +61473,23 @@
       </c>
       <c r="AP308" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR308" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS308" t="inlineStr"/>
       <c r="AT308" t="n">
         <v>0</v>
       </c>
+      <c r="AU308" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV308" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -62132,6 +62642,11 @@
       <c r="Q314" t="n">
         <v>0</v>
       </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA314" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62144,13 +62659,23 @@
       </c>
       <c r="AP314" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR314" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS314" t="inlineStr"/>
       <c r="AT314" t="n">
         <v>0</v>
       </c>
+      <c r="AU314" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV314" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -63303,6 +63828,11 @@
       <c r="Q320" t="n">
         <v>0</v>
       </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA320" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63315,12 +63845,22 @@
       </c>
       <c r="AP320" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR320" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS320" t="inlineStr"/>
       <c r="AT320" t="n">
         <v>0</v>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV320" t="inlineStr">
         <is>
